--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -165,10 +165,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +557 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +2 814 €/mois.</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
           <t>Loyer mensuel HT</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
-        <v>1895.83</v>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>ESTIMATION au loyer de marché local — aucun bail ne le garantit</t>
+      <c r="B20" s="17" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>loyer du bail en place (à faire confirmer par le bail)</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
           <t>4 202 à 7 660 €/m²</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>ce bien est 48 % SOUS la médiane locale</t>
         </is>
@@ -1035,7 +1035,7 @@
           <t>226 ventes réelles 2023-2025 (DVF)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>DVF = prix réellement payés, enregistrés chez le notaire (data.gouv.fr)</t>
         </is>
@@ -1054,10 +1054,10 @@
           <t>Prix négocié retenu</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="19" t="n">
         <v>190000</v>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>par défaut le prix affiché — un prix demandé se négocie</t>
         </is>
@@ -1112,7 +1112,7 @@
       <c r="B30" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>à remplacer par le montant réel dès que connu</t>
         </is>
@@ -1134,7 +1134,7 @@
           <t>Assurance propriétaire (PNO, €/an)</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="19" t="n">
         <v>300</v>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         <f>B25*(1+B26)</f>
         <v/>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>prix négocié + frais d'acquisition</t>
         </is>
@@ -1299,7 +1299,7 @@
         <f>B48/12</f>
         <v/>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>positif : le bien se paie tout seul, loyer ≥ crédit + charges</t>
         </is>
@@ -1322,7 +1322,7 @@
         <f>IFERROR(B42/B25,"")</f>
         <v/>
       </c>
-      <c r="C52" s="19" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
@@ -1338,7 +1338,7 @@
         <f>IFERROR(B46/B35,"")</f>
         <v/>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>après taxe foncière, entretien et assurance</t>
         </is>
@@ -1354,7 +1354,7 @@
         <f>IFERROR(B46/B39,"")</f>
         <v/>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
         </is>
@@ -1370,7 +1370,7 @@
         <f>IFERROR(B37/B25,"")</f>
         <v/>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C55" s="18" t="inlineStr">
         <is>
           <t>≤ 80 % est la zone de confort bancaire</t>
         </is>
@@ -1398,7 +1398,7 @@
           <t>64/100</t>
         </is>
       </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>rendement, emplacement, prix vs marché, financement, fiscalité</t>
         </is>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +2 814 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +2 801 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
+++ b/docs/dossiers/dossier-paris-19e-92d3491f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
